--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -76,82 +76,64 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
     <t>ESCOBAR</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>TEPOLE</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
     <t>ANGELES</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>TETLACTLE</t>
   </si>
   <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>ROCHA</t>
   </si>
   <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>JONATAN GILBERTO</t>
+  </si>
+  <si>
+    <t>JOSE</t>
   </si>
   <si>
     <t>LUZ ALONDRA</t>
   </si>
   <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
     <t>JONATHAN</t>
   </si>
   <si>
     <t>BRENDA JANELY</t>
   </si>
   <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
     <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>KARYME CONCEPCION</t>
-  </si>
-  <si>
-    <t>ALDO</t>
   </si>
 </sst>
 </file>
@@ -549,7 +531,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -558,10 +540,10 @@
         <v>8</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>78.38</v>
+        <v>77.78</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -692,19 +674,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -718,16 +703,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -741,16 +729,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H4">
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -764,16 +755,19 @@
         <v>30</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>30</v>
       </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -823,22 +817,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>78.38</v>
+        <v>75</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -855,16 +849,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -890,7 +884,7 @@
         <v>84.62</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -916,7 +910,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +920,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,16 +952,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920237</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -981,22 +975,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920369</v>
+        <v>22330051920405</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1004,22 +998,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920256</v>
+        <v>22330051920273</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1027,16 +1021,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920259</v>
+        <v>22330051920237</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1045,53 +1039,53 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920405</v>
+        <v>22330051920256</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920273</v>
+        <v>22330051920259</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1102,10 +1096,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1114,52 +1108,6 @@
         <v>11</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920211</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920272</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -76,9 +76,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>ANGELES</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -113,9 +107,6 @@
   </si>
   <si>
     <t>ROCHA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
   </si>
   <si>
     <t>JONATAN GILBERTO</t>
@@ -920,7 +911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -952,22 +943,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920405</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -975,16 +966,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920405</v>
+        <v>22330051920273</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -998,39 +989,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920273</v>
+        <v>22330051920237</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920237</v>
+        <v>22330051920256</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1044,16 +1035,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920256</v>
+        <v>22330051920259</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1067,47 +1058,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920259</v>
+        <v>21330051920002</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920002</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -76,55 +76,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>APALE</t>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>TETLACTLE</t>
   </si>
   <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>JONATAN GILBERTO</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>AILYN</t>
   </si>
   <si>
     <t>JONATHAN</t>
   </si>
   <si>
-    <t>BRENDA JANELY</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
+    <t>EVELYN ROSALIA</t>
   </si>
 </sst>
 </file>
@@ -814,13 +799,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>80.56</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -840,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
         <v>7.8</v>
@@ -866,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>84.62</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -901,7 +886,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -943,22 +928,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920405</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -966,39 +951,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920273</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920237</v>
+        <v>22330051920256</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1012,70 +997,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920256</v>
+        <v>22330051920222</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920259</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920002</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -79,34 +79,43 @@
     <t>DECTOR</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
     <t>PALACIOS</t>
   </si>
   <si>
     <t>KEVIN ALEXIS</t>
   </si>
   <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>LILIANA</t>
+  </si>
+  <si>
     <t>AILYN</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
   </si>
   <si>
     <t>EVELYN ROSALIA</t>
@@ -565,16 +574,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>84.62</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -717,7 +726,7 @@
         <v>84.62</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -799,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>80.56</v>
+        <v>83.33</v>
       </c>
       <c r="H2">
         <v>6.9</v>
@@ -860,7 +869,7 @@
         <v>88.45999999999999</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -896,7 +905,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,10 +943,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -951,16 +960,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>21330051420317</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -969,52 +978,75 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920256</v>
+        <v>22330051920213</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920222</v>
+        <v>22330051920366</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920222</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,12 @@
     <t>LLANOS</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -97,6 +97,9 @@
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>JOSE</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -110,6 +113,9 @@
   </si>
   <si>
     <t>SERGIO</t>
+  </si>
+  <si>
+    <t>HECTOR MISAEL</t>
   </si>
   <si>
     <t>LILIANA</t>
@@ -905,7 +911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -946,7 +952,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -969,7 +975,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -983,7 +989,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920213</v>
+        <v>22330051920279</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -992,13 +998,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1006,7 +1012,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920366</v>
+        <v>22330051920213</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -1015,38 +1021,61 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920222</v>
+        <v>22330051920366</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920222</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>11</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
@@ -823,7 +823,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -849,7 +849,7 @@
         <v>87.5</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -875,7 +875,7 @@
         <v>88.45999999999999</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -901,7 +901,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20231.xlsx
@@ -823,7 +823,7 @@
         <v>83.33</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -849,7 +849,7 @@
         <v>87.5</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -875,7 +875,7 @@
         <v>88.45999999999999</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -901,7 +901,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
